--- a/ToxCast_model/experiments/prediction/DART_MTL_251228/DART_MTL_seed1val/score_seed1val.xlsx
+++ b/ToxCast_model/experiments/prediction/DART_MTL_251228/DART_MTL_seed1val/score_seed1val.xlsx
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.6810646376464961</v>
+        <v>0.6810048433389141</v>
       </c>
       <c r="E190" t="n">
         <v>0.8468085106382979</v>
@@ -8837,7 +8837,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>0.877200163733115</v>
+        <v>0.8772001637331149</v>
       </c>
       <c r="E241" t="n">
         <v>0.9929078014184397</v>
